--- a/estimate/聖建様_特別教育eラーニング_概算見積.xlsx
+++ b/estimate/聖建様_特別教育eラーニング_概算見積.xlsx
@@ -13,6 +13,7 @@
     <sheet name="03_教材制作費" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="04_システム費用" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="05_前提・責任分界" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="06_講師・監修者台帳" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -65,7 +66,55 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">労働安全衛生コンサルタント等の第三者監修。法定の科目・範囲・時間を満たしていることを、監修者名を明示して確認します。</t>
+          <t xml:space="preserve">聖建様の社内有資格者が監修される前提のため </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">円としています。外部の労働安全衛生コンサルタント等に依頼される場合は </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">350,000 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">円程度を目安に入力してください。監修者の氏名・保有資格はシート</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">06</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">の台帳に記録します。</t>
         </r>
       </text>
     </comment>
@@ -86,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="246">
   <si>
     <r>
       <rPr>
@@ -1777,7 +1826,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">専門家による監修費（</t>
+      <t xml:space="preserve">監修費（</t>
     </r>
     <r>
       <rPr>
@@ -1802,7 +1851,72 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">労働安全衛生コンサルタント等の第三者監修。法定の科目・範囲・時間を満たしていることを、監修者名を明示して確認します。</t>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">聖建様の社内有資格者が監修される前提のため </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円としています。外部の労働安全衛生コンサルタント等に依頼される場合は </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">350,000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円程度を目安に入力してください。監修者の氏名・保有資格はシート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の台帳に記録します。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2249,7 +2363,47 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">第三者の専門家が監修し、法定の科目・範囲・時間を満たしていることを監修者名を明示して確認します。</t>
+      <t xml:space="preserve">聖建様の社内有資格者が監修し、内容が現場の実態と合っているかを確認します（法令への当てはめは弊社が行います）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監修者の氏名・保有資格・レビュー日をシート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の台帳に記録し、監督署への説明資料とします。</t>
     </r>
   </si>
   <si>
@@ -2370,7 +2524,153 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">割程度を想定してください（監修費は科目ごとに必要です）。</t>
+      <t xml:space="preserve">割程度を想定してください。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF16324F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 監修について（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF16324F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF16324F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF16324F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF16324F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF16324F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9.5"/>
+        <color rgb="FF16324F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日の打合せを反映）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">・聖建様の社内に、科目に対応する有資格者・実務経験者がいらっしゃるため、外部コンサルタントの監修費は計上していません。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・かわりに、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監修者の資格を修了証の写しで確認、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">章立て設計の段階で所轄労働基準監督署へ事前相談（無料）、の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点を実施します。</t>
     </r>
   </si>
   <si>
@@ -3057,14 +3357,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">教材内容の監修について</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">・教材の法令適合性を確認できる専門家（労働安全衛生コンサルタント等）は、弊社が手配し、費用に含めてご提示します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">・聖建様に、監修内容をご自身で調査・判断していただく必要はありません。</t>
+      <t xml:space="preserve">教材内容の監修について（社内監修を前提とします）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">・聖建様の社内に、科目に対応する有資格者・実務経験者がいらっしゃるため、外部コンサルタントの監修は不要と判断しました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・弊社が担うのは「法令への当てはめ」です。安全衛生特別教育規程の原典から科目・範囲・時間を書き出し、それを満たす章立てと尺を設計します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・聖建様の監修者に担っていただくのは「内容が現場の実態と合っているか」の確認です。法令の条文を調べていただく必要はありません。</t>
   </si>
   <si>
     <r>
@@ -3074,7 +3377,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・ただし、監修は無償では行えません。</t>
+      <t xml:space="preserve">・監修者の氏名・保有資格・修了証の確認状況・台本のレビュー日を、シート</t>
     </r>
     <r>
       <rPr>
@@ -3084,7 +3387,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">06</t>
     </r>
     <r>
       <rPr>
@@ -3093,14 +3396,23 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">科目あたりの監修費として、お見積りに計上させていただきます。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">・監修者の氏名・資格は教材内および修了証に明示します。これにより、第三者から根拠を問われた際に示せる状態になります。</t>
+      <t xml:space="preserve">の台帳に記録します。これが監督署への説明資料になります。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 注意：特別教育を「受講した経験」だけでは、講師要件の裏付けとしては弱くなります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　 科目に対応する作業主任者技能講習の修了証、または免許の保有を、現物の写しでご確認ください（費用はかかりません）。</t>
   </si>
   <si>
     <t xml:space="preserve">・弁護士による確認では代替できません。労働安全衛生教育の内容の妥当性は、法律実務ではなく安全衛生の専門領域だからです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・章立ての設計が固まった段階で、所轄の労働基準監督署（半田市の事業場は半田労働基準監督署）へ事前相談を行います。無料です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　 特別教育には登録・認可の制度がないため、事前にお墨付きを得る窓口は存在しません。相談の記録を残すことが、実務上の最善策になります。</t>
   </si>
   <si>
     <r>
@@ -3696,6 +4008,389 @@
   </si>
   <si>
     <t xml:space="preserve">・各科目の時間数は、上記規程および複数の講習機関が公表するカリキュラムで相互に確認しています。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">講師・監修者 台帳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特別教育の講師に法定の資格要件はありませんが、「教習科目について十分な知識と経験を有する者」であることの説明が求められます。その説明資料がこの台帳です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">科目（業務の名称）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監修者
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">講師</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">所属・役職</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保有資格 ①（科目に対応するもの）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資格番号・取得年月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保有資格 ②</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実務
+経験年数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">修了証写し
+の確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台本レビュー
+完了日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">監修者の署名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【記入例】足場の組立て等の業務</t>
+  </si>
+  <si>
+    <t xml:space="preserve">山田 太郎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">聖建 工事部 部長</t>
+  </si>
+  <si>
+    <t xml:space="preserve">足場の組立て等作業主任者技能講習 修了</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12345</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 2015</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">職長・安全衛生責任者教育 修了</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">済 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6B7B8A"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-09-10)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 科目ごとに、どの資格が説明力を持つか</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　足場の組立て等　　　　　→　足場の組立て等作業主任者技能講習 修了者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　石綿等の解体等　　　　　→　石綿作業主任者技能講習 修了者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　酸素欠乏・硫化水素　　　→　酸素欠乏・硫化水素危険作業主任者技能講習 修了者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　低圧電気取扱　　　　　　→　第一種／第二種電気工事士、電気主任技術者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　粉じん作業　　　　　　　→　特定粉じん作業に係る実務経験、じん肺関係の教育歴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　フルハーネス　　　　　　→　建築物等の鉄骨の組立て等作業主任者、または高所作業の実務経験＋教育歴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　テールゲートリフター　　→　当該機器の操作実務経験、荷役作業の教育歴</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　共通して強い資格　　　　→　労働安全衛生コンサルタント（安全／衛生）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">講座 修了者</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">■ この台帳の使い方</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・黄色のセルにご記入ください。科目名はシート</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">から自動で入ります。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">・「修了証写しの確認」は、現物の写しを実際に確認した日を記入します。「持っているはず」では監督署に説明できません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・「台本レビュー完了日」は、監修者が実際に台本を読んで確認した日です。名前だけを載せる名義貸しは、講師要件を満たしたことになりません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・監修者の署名（または押印）を得て、教材ごとに保管してください。教材内および修了証にも監修者名を明示します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 根拠</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・昭和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">48</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日 基発第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">145</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF4A5A68"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号：「特別教育の講師については法令で資格要件は定められていないが、</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　教習科目について十分な知識、経験を有する者でなければならないことは当然である」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・特別教育には登録・認可の制度がありません。事前に届け出る窓口はなく、労働基準監督署の臨検で事後的に確認されます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・そのため、この台帳と台本のレビュー記録が、実務上ほぼ唯一の説明手段になります。</t>
   </si>
 </sst>
 </file>
@@ -3708,7 +4403,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;時間&quot;;;\-"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="51">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4030,6 +4725,31 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF6B7B8A"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF6B7B8A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF008000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFB3402F"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -4112,7 +4832,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4326,6 +5046,38 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4622,11 +5374,11 @@
       </c>
       <c r="C5" s="7" t="n">
         <f aca="false">03_教材制作費!H31</f>
-        <v>5035000</v>
+        <v>3985000</v>
       </c>
       <c r="D5" s="7" t="n">
         <f aca="false">03_教材制作費!H31</f>
-        <v>5035000</v>
+        <v>3985000</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>7</v>
@@ -4673,11 +5425,11 @@
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">SUM(C5:C7)</f>
-        <v>8435000</v>
+        <v>7385000</v>
       </c>
       <c r="D8" s="11" t="n">
         <f aca="false">SUM(D5:D7)</f>
-        <v>10935000</v>
+        <v>9885000</v>
       </c>
       <c r="E8" s="9"/>
     </row>
@@ -4688,11 +5440,11 @@
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">C5+C6</f>
-        <v>7235000</v>
+        <v>6185000</v>
       </c>
       <c r="D9" s="12" t="n">
         <f aca="false">D5+D6</f>
-        <v>8835000</v>
+        <v>7785000</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>14</v>
@@ -5235,7 +5987,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5280,7 +6032,7 @@
         <v>87</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="29" t="s">
@@ -5421,7 +6173,7 @@
       </c>
       <c r="F17" s="32" t="n">
         <f aca="false">IF($A17=1,$C$6,0)</f>
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G17" s="32" t="n">
         <f aca="false">IF($A17=1,$C$7,0)</f>
@@ -5429,7 +6181,7 @@
       </c>
       <c r="H17" s="36" t="n">
         <f aca="false">SUM(E17:G17)</f>
-        <v>1970000</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5553,7 +6305,7 @@
       </c>
       <c r="F21" s="32" t="n">
         <f aca="false">IF($A21=1,$C$6,0)</f>
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="32" t="n">
         <f aca="false">IF($A21=1,$C$7,0)</f>
@@ -5561,7 +6313,7 @@
       </c>
       <c r="H21" s="36" t="n">
         <f aca="false">SUM(E21:G21)</f>
-        <v>1595000</v>
+        <v>1245000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5586,7 +6338,7 @@
       </c>
       <c r="F22" s="32" t="n">
         <f aca="false">IF($A22=1,$C$6,0)</f>
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G22" s="32" t="n">
         <f aca="false">IF($A22=1,$C$7,0)</f>
@@ -5594,7 +6346,7 @@
       </c>
       <c r="H22" s="36" t="n">
         <f aca="false">SUM(E22:G22)</f>
-        <v>1470000</v>
+        <v>1120000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5880,7 +6632,7 @@
       </c>
       <c r="F31" s="41" t="n">
         <f aca="false">SUM(F17:F30)</f>
-        <v>1050000</v>
+        <v>0</v>
       </c>
       <c r="G31" s="41" t="n">
         <f aca="false">SUM(G17:G30)</f>
@@ -5888,7 +6640,7 @@
       </c>
       <c r="H31" s="41" t="n">
         <f aca="false">SUM(H17:H30)</f>
-        <v>5035000</v>
+        <v>3985000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5922,21 +6674,44 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18"/>
+      <c r="A39" s="42" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43" t="s">
-        <v>114</v>
-      </c>
+      <c r="A40" s="18"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="43" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -5975,20 +6750,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
@@ -6002,10 +6777,10 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C5" s="45" t="n">
         <v>400000</v>
@@ -6014,15 +6789,15 @@
         <v>700000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C6" s="45" t="n">
         <v>500000</v>
@@ -6031,15 +6806,15 @@
         <v>800000</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C7" s="45" t="n">
         <v>450000</v>
@@ -6048,15 +6823,15 @@
         <v>800000</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C8" s="45" t="n">
         <v>400000</v>
@@ -6065,15 +6840,15 @@
         <v>700000</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C9" s="45" t="n">
         <v>250000</v>
@@ -6082,15 +6857,15 @@
         <v>450000</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C10" s="45" t="n">
         <v>200000</v>
@@ -6099,15 +6874,15 @@
         <v>350000</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C11" s="45" t="n">
         <v>400000</v>
@@ -6116,15 +6891,15 @@
         <v>700000</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C12" s="45" t="n">
         <v>250000</v>
@@ -6133,15 +6908,15 @@
         <v>450000</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C13" s="45" t="n">
         <v>350000</v>
@@ -6150,15 +6925,15 @@
         <v>600000</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C14" s="45" t="n">
         <v>200000</v>
@@ -6167,13 +6942,13 @@
         <v>350000</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40"/>
       <c r="B15" s="38" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C15" s="41" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -6188,7 +6963,7 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40"/>
       <c r="B16" s="38" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C16" s="41" t="n">
         <f aca="false">SUM(C11:C14)</f>
@@ -6203,7 +6978,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9"/>
       <c r="B17" s="47" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C17" s="48" t="n">
         <f aca="false">C15+C16</f>
@@ -6217,7 +6992,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6226,10 +7001,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>94</v>
@@ -6238,7 +7013,7 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
       <c r="B21" s="31" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C21" s="45" t="n">
         <v>20000</v>
@@ -6247,13 +7022,13 @@
         <v>40000</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
       <c r="B22" s="31" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C22" s="45" t="n">
         <v>30000</v>
@@ -6262,13 +7037,13 @@
         <v>50000</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="31" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C23" s="45" t="n">
         <v>0</v>
@@ -6277,13 +7052,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
       <c r="B24" s="31" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C24" s="45" t="n">
         <v>0</v>
@@ -6292,13 +7067,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="40"/>
       <c r="B25" s="38" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C25" s="41" t="n">
         <f aca="false">SUM(C21:C24)</f>
@@ -6312,17 +7087,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -6341,7 +7116,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -6350,37 +7125,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="49" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="50" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="51" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="51" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="51" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6388,157 +7163,596 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="52" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="51" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="51" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="51" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="51" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="49" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="51" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="51" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="51" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="51" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="53" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="49" t="s">
-        <v>179</v>
+      <c r="B21" s="51"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="53" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="53" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="53" t="s">
-        <v>180</v>
-      </c>
+      <c r="B24" s="51"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="53" t="s">
-        <v>181</v>
+      <c r="B25" s="51" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="50" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="49" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="51" t="s">
-        <v>184</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="49" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="51" t="s">
-        <v>185</v>
+      <c r="B30" s="53" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="53" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="49" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="51" t="s">
-        <v>188</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="49" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="51" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="51" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="51" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="51" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="49" t="s">
-        <v>193</v>
+      <c r="B37" s="53" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="51" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="51" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="51" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="51" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="51" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="51" t="s">
-        <v>198</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="49" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="51" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="51" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="51" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="51" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="51" t="s">
+        <v>206</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="G5" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>226</v>
+      </c>
+      <c r="J5" s="57"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="58" t="str">
+        <f aca="false">02_科目マスタ!A5</f>
+        <v>足場の組立て等の業務</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="58" t="str">
+        <f aca="false">02_科目マスタ!A6</f>
+        <v>粉じん作業に係る業務</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="58" t="str">
+        <f aca="false">02_科目マスタ!A7</f>
+        <v>石綿等が使用されている建築物等の解体等の業務</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="58" t="str">
+        <f aca="false">02_科目マスタ!A8</f>
+        <v>酸素欠乏・硫化水素危険作業（第2種）</v>
+      </c>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="58" t="str">
+        <f aca="false">02_科目マスタ!A9</f>
+        <v>フルハーネス型墜落制止用器具を用いて行う作業</v>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="58" t="str">
+        <f aca="false">02_科目マスタ!A10</f>
+        <v>テールゲートリフターの操作の業務</v>
+      </c>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="58" t="str">
+        <f aca="false">02_科目マスタ!A11</f>
+        <v>自由研削といしの取替え等の業務</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="58" t="str">
+        <f aca="false">02_科目マスタ!A12</f>
+        <v>低圧電気取扱業務（開閉器の操作のみ）</v>
+      </c>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="58" t="str">
+        <f aca="false">02_科目マスタ!A13</f>
+        <v>低圧電気取扱業務（充電電路の敷設等）</v>
+      </c>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="58" t="str">
+        <f aca="false">02_科目マスタ!A14</f>
+        <v>高所作業車の運転（作業床の高さ10m未満）</v>
+      </c>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="58" t="str">
+        <f aca="false">02_科目マスタ!A15</f>
+        <v>玉掛けの業務（つり上げ荷重1トン未満）</v>
+      </c>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="58" t="str">
+        <f aca="false">02_科目マスタ!A16</f>
+        <v>小型車両系建設機械の運転（機体重量3トン未満）</v>
+      </c>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="58" t="str">
+        <f aca="false">02_科目マスタ!A17</f>
+        <v>チェーンソーを用いて行う伐木等の業務</v>
+      </c>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="58" t="str">
+        <f aca="false">02_科目マスタ!A18</f>
+        <v>アーク溶接等の業務</v>
+      </c>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="61" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="61" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
